--- a/backend/data/financials_by_company/002045.SZ.xlsx
+++ b/backend/data/financials_by_company/002045.SZ.xlsx
@@ -677,616 +677,616 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-7578143</v>
+        <v>14395159.205</v>
       </c>
       <c r="C2" t="n">
         <v>0.25</v>
       </c>
       <c r="D2" t="n">
-        <v>493071725.36</v>
+        <v>84307652.84999999</v>
       </c>
       <c r="E2" t="n">
-        <v>-30312572</v>
+        <v>57580636.82</v>
       </c>
       <c r="F2" t="n">
-        <v>-30312572</v>
+        <v>57580636.82</v>
       </c>
       <c r="G2" t="n">
-        <v>252977351.75</v>
+        <v>40136849.48</v>
       </c>
       <c r="H2" t="n">
-        <v>175732750.42</v>
+        <v>124707345.83</v>
       </c>
       <c r="I2" t="n">
-        <v>6846528718.25</v>
+        <v>4332996852.05</v>
       </c>
       <c r="J2" t="n">
-        <v>462759153.36</v>
+        <v>141888289.67</v>
       </c>
       <c r="K2" t="n">
-        <v>287026402.94</v>
+        <v>17180943.84</v>
       </c>
       <c r="L2" t="n">
-        <v>25158566.77</v>
+        <v>6472145.98</v>
       </c>
       <c r="M2" t="n">
-        <v>54552980.44</v>
+        <v>907210.6800000001</v>
       </c>
       <c r="N2" t="n">
-        <v>81637102.75</v>
+        <v>8331958.54</v>
       </c>
       <c r="O2" t="n">
-        <v>275711780.75</v>
+        <v>-3048628.135</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>7740229904.03</v>
+        <v>4827301012.07</v>
       </c>
       <c r="R2" t="n">
-        <v>231410568.11</v>
+        <v>14747528.24</v>
       </c>
       <c r="S2" t="n">
-        <v>549950765</v>
+        <v>445964994</v>
       </c>
       <c r="T2" t="n">
-        <v>549950765</v>
+        <v>445964994</v>
       </c>
       <c r="U2" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="V2" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="W2" t="n">
-        <v>252977351.75</v>
+        <v>40136849.48</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>252977351.75</v>
+        <v>40136849.48</v>
       </c>
       <c r="Z2" t="n">
-        <v>-720263.61</v>
+        <v>-66027.3</v>
       </c>
       <c r="AA2" t="n">
-        <v>253697615.36</v>
+        <v>40202876.78</v>
       </c>
       <c r="AB2" t="n">
-        <v>253697615.36</v>
+        <v>40202876.78</v>
       </c>
       <c r="AC2" t="n">
-        <v>-21224192.86</v>
+        <v>-23929143.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>232473422.5</v>
+        <v>16273733.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>1062854.39</v>
+        <v>-29554535.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>-31458607.95</v>
+        <v>-9535627</v>
       </c>
       <c r="AG2" t="n">
-        <v>836966.84</v>
+        <v>-7980451.26</v>
       </c>
       <c r="AH2" t="n">
-        <v>17017784.97</v>
+        <v>1722126.24</v>
       </c>
       <c r="AI2" t="n">
-        <v>13603856.14</v>
+        <v>15793952.02</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25158566.77</v>
+        <v>6472145.98</v>
       </c>
       <c r="AK2" t="n">
-        <v>1925555.54</v>
+        <v>952601.88</v>
       </c>
       <c r="AL2" t="n">
-        <v>54552980.44</v>
+        <v>907210.6800000001</v>
       </c>
       <c r="AM2" t="n">
-        <v>81637102.75</v>
+        <v>8331958.54</v>
       </c>
       <c r="AN2" t="n">
-        <v>161112979.1</v>
+        <v>-11915102.26</v>
       </c>
       <c r="AO2" t="n">
-        <v>893701185.78</v>
+        <v>494304160.02</v>
       </c>
       <c r="AP2" t="n">
-        <v>35759423.21</v>
+        <v>28073861.71</v>
       </c>
       <c r="AQ2" t="n">
-        <v>40311911.35</v>
+        <v>28357337.87</v>
       </c>
       <c r="AR2" t="n">
-        <v>40311911.35</v>
+        <v>28357337.87</v>
       </c>
       <c r="AS2" t="n">
-        <v>455089715.18</v>
+        <v>252387263.32</v>
       </c>
       <c r="AT2" t="n">
-        <v>104798550.33</v>
+        <v>51984818.54</v>
       </c>
       <c r="AU2" t="n">
-        <v>49142916.21</v>
+        <v>13199903.16</v>
       </c>
       <c r="AV2" t="n">
-        <v>55655634.12</v>
+        <v>38784915.38</v>
       </c>
       <c r="AW2" t="n">
-        <v>1054814164.88</v>
+        <v>482389057.76</v>
       </c>
       <c r="AX2" t="n">
-        <v>6846528718.25</v>
+        <v>4332996852.05</v>
       </c>
       <c r="AY2" t="n">
-        <v>7901342883.13</v>
+        <v>4815385909.81</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-14737718.1225</v>
+        <v>-23539718.205</v>
       </c>
       <c r="C3" t="n">
         <v>0.25</v>
       </c>
       <c r="D3" t="n">
-        <v>602047708.96</v>
+        <v>447831120.61</v>
       </c>
       <c r="E3" t="n">
-        <v>-58950872.49</v>
+        <v>-94158872.81999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-58950872.49</v>
+        <v>-94158872.81999999</v>
       </c>
       <c r="G3" t="n">
-        <v>360706130.18</v>
+        <v>178323752.76</v>
       </c>
       <c r="H3" t="n">
-        <v>153727732.91</v>
+        <v>149628265.88</v>
       </c>
       <c r="I3" t="n">
-        <v>5039668822.17</v>
+        <v>5256657442.19</v>
       </c>
       <c r="J3" t="n">
-        <v>543096836.47</v>
+        <v>353672247.79</v>
       </c>
       <c r="K3" t="n">
-        <v>389369103.56</v>
+        <v>204043981.91</v>
       </c>
       <c r="L3" t="n">
-        <v>-2369297.33</v>
+        <v>-32390012.8</v>
       </c>
       <c r="M3" t="n">
-        <v>39207629.41</v>
+        <v>41393874.12</v>
       </c>
       <c r="N3" t="n">
-        <v>37111000.04</v>
+        <v>10382723.58</v>
       </c>
       <c r="O3" t="n">
-        <v>404919284.5475</v>
-      </c>
-      <c r="P3" t="inlineStr"/>
+        <v>248942907.375</v>
+      </c>
+      <c r="P3" t="n">
+        <v>178323752.76</v>
+      </c>
       <c r="Q3" t="n">
-        <v>5650455254.08</v>
+        <v>5797414478.56</v>
       </c>
       <c r="R3" t="n">
-        <v>345704234.24</v>
+        <v>157172466.79</v>
       </c>
       <c r="S3" t="n">
-        <v>462443757</v>
+        <v>445809382</v>
       </c>
       <c r="T3" t="n">
-        <v>462443757</v>
+        <v>445809382</v>
       </c>
       <c r="U3" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="V3" t="n">
-        <v>0.78</v>
+        <v>0.4</v>
       </c>
       <c r="W3" t="n">
-        <v>360706130.18</v>
+        <v>178323752.76</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>360706130.18</v>
+        <v>178323752.76</v>
       </c>
       <c r="Z3" t="n">
-        <v>-253941.63</v>
+        <v>-661433.36</v>
       </c>
       <c r="AA3" t="n">
-        <v>360960071.81</v>
+        <v>178985186.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>360960071.81</v>
+        <v>178985186.12</v>
       </c>
       <c r="AC3" t="n">
-        <v>-10798597.66</v>
+        <v>-16335078.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>350161474.15</v>
+        <v>162650107.79</v>
       </c>
       <c r="AE3" t="n">
-        <v>4457239.91</v>
+        <v>5477641</v>
       </c>
       <c r="AF3" t="n">
-        <v>-19118600.8</v>
+        <v>-52102714.43</v>
       </c>
       <c r="AG3" t="n">
-        <v>-4899831.36</v>
+        <v>-1830977.03</v>
       </c>
       <c r="AH3" t="n">
-        <v>-7633093.97</v>
+        <v>14071381.64</v>
       </c>
       <c r="AI3" t="n">
-        <v>31651526.13</v>
+        <v>39862309.82</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-2369297.33</v>
+        <v>-32390012.8</v>
       </c>
       <c r="AK3" t="n">
-        <v>272667.96</v>
+        <v>1378862.26</v>
       </c>
       <c r="AL3" t="n">
-        <v>39207629.41</v>
+        <v>41393874.12</v>
       </c>
       <c r="AM3" t="n">
-        <v>37111000.04</v>
+        <v>10382723.58</v>
       </c>
       <c r="AN3" t="n">
-        <v>282715038.97</v>
+        <v>196304575.2</v>
       </c>
       <c r="AO3" t="n">
-        <v>610786431.91</v>
+        <v>540757036.37</v>
       </c>
       <c r="AP3" t="n">
-        <v>30092050.68</v>
+        <v>32799391.48</v>
       </c>
       <c r="AQ3" t="n">
-        <v>34134823.59</v>
+        <v>32119851.23</v>
       </c>
       <c r="AR3" t="n">
-        <v>34134823.59</v>
+        <v>32119851.23</v>
       </c>
       <c r="AS3" t="n">
-        <v>318977654.08</v>
+        <v>273529959.14</v>
       </c>
       <c r="AT3" t="n">
-        <v>66923600.15</v>
+        <v>54301122.26</v>
       </c>
       <c r="AU3" t="n">
-        <v>23755618.57</v>
+        <v>12290583.87</v>
       </c>
       <c r="AV3" t="n">
-        <v>43167981.58</v>
+        <v>42010538.39</v>
       </c>
       <c r="AW3" t="n">
-        <v>893501470.88</v>
+        <v>737061611.5700001</v>
       </c>
       <c r="AX3" t="n">
-        <v>5039668822.17</v>
+        <v>5256657442.19</v>
       </c>
       <c r="AY3" t="n">
-        <v>5933170293.05</v>
+        <v>5993719053.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-23539718.205</v>
+        <v>-14737718.1225</v>
       </c>
       <c r="C4" t="n">
         <v>0.25</v>
       </c>
       <c r="D4" t="n">
-        <v>447831120.61</v>
+        <v>602047708.96</v>
       </c>
       <c r="E4" t="n">
-        <v>-94158872.81999999</v>
+        <v>-58950872.49</v>
       </c>
       <c r="F4" t="n">
-        <v>-94158872.81999999</v>
+        <v>-58950872.49</v>
       </c>
       <c r="G4" t="n">
-        <v>178323752.76</v>
+        <v>360706130.18</v>
       </c>
       <c r="H4" t="n">
-        <v>149628265.88</v>
+        <v>153727732.91</v>
       </c>
       <c r="I4" t="n">
-        <v>5256657442.19</v>
+        <v>5039668822.17</v>
       </c>
       <c r="J4" t="n">
-        <v>353672247.79</v>
+        <v>543096836.47</v>
       </c>
       <c r="K4" t="n">
-        <v>204043981.91</v>
+        <v>389369103.56</v>
       </c>
       <c r="L4" t="n">
-        <v>-32390012.8</v>
+        <v>-2369297.33</v>
       </c>
       <c r="M4" t="n">
-        <v>41393874.12</v>
+        <v>39207629.41</v>
       </c>
       <c r="N4" t="n">
-        <v>10382723.58</v>
+        <v>37111000.04</v>
       </c>
       <c r="O4" t="n">
-        <v>248942907.375</v>
-      </c>
-      <c r="P4" t="n">
-        <v>178323752.76</v>
-      </c>
+        <v>404919284.5475</v>
+      </c>
+      <c r="P4" t="inlineStr"/>
       <c r="Q4" t="n">
-        <v>5797414478.56</v>
+        <v>5650455254.08</v>
       </c>
       <c r="R4" t="n">
-        <v>157172466.79</v>
+        <v>345704234.24</v>
       </c>
       <c r="S4" t="n">
-        <v>445809382</v>
+        <v>462443757</v>
       </c>
       <c r="T4" t="n">
-        <v>445809382</v>
+        <v>462443757</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.78</v>
       </c>
       <c r="W4" t="n">
-        <v>178323752.76</v>
+        <v>360706130.18</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>178323752.76</v>
+        <v>360706130.18</v>
       </c>
       <c r="Z4" t="n">
-        <v>-661433.36</v>
+        <v>-253941.63</v>
       </c>
       <c r="AA4" t="n">
-        <v>178985186.12</v>
+        <v>360960071.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>178985186.12</v>
+        <v>360960071.81</v>
       </c>
       <c r="AC4" t="n">
-        <v>-16335078.33</v>
+        <v>-10798597.66</v>
       </c>
       <c r="AD4" t="n">
-        <v>162650107.79</v>
+        <v>350161474.15</v>
       </c>
       <c r="AE4" t="n">
-        <v>5477641</v>
+        <v>4457239.91</v>
       </c>
       <c r="AF4" t="n">
-        <v>-52102714.43</v>
+        <v>-19118600.8</v>
       </c>
       <c r="AG4" t="n">
-        <v>-1830977.03</v>
+        <v>-4899831.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>14071381.64</v>
+        <v>-7633093.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>39862309.82</v>
+        <v>31651526.13</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-32390012.8</v>
+        <v>-2369297.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1378862.26</v>
+        <v>272667.96</v>
       </c>
       <c r="AL4" t="n">
-        <v>41393874.12</v>
+        <v>39207629.41</v>
       </c>
       <c r="AM4" t="n">
-        <v>10382723.58</v>
+        <v>37111000.04</v>
       </c>
       <c r="AN4" t="n">
-        <v>196304575.2</v>
+        <v>282715038.97</v>
       </c>
       <c r="AO4" t="n">
-        <v>540757036.37</v>
+        <v>610786431.91</v>
       </c>
       <c r="AP4" t="n">
-        <v>32799391.48</v>
+        <v>30092050.68</v>
       </c>
       <c r="AQ4" t="n">
-        <v>32119851.23</v>
+        <v>34134823.59</v>
       </c>
       <c r="AR4" t="n">
-        <v>32119851.23</v>
+        <v>34134823.59</v>
       </c>
       <c r="AS4" t="n">
-        <v>273529959.14</v>
+        <v>318977654.08</v>
       </c>
       <c r="AT4" t="n">
-        <v>54301122.26</v>
+        <v>66923600.15</v>
       </c>
       <c r="AU4" t="n">
-        <v>12290583.87</v>
+        <v>23755618.57</v>
       </c>
       <c r="AV4" t="n">
-        <v>42010538.39</v>
+        <v>43167981.58</v>
       </c>
       <c r="AW4" t="n">
-        <v>737061611.5700001</v>
+        <v>893501470.88</v>
       </c>
       <c r="AX4" t="n">
-        <v>5256657442.19</v>
+        <v>5039668822.17</v>
       </c>
       <c r="AY4" t="n">
-        <v>5993719053.76</v>
+        <v>5933170293.05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>14395159.205</v>
+        <v>-7578143</v>
       </c>
       <c r="C5" t="n">
         <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>84307652.84999999</v>
+        <v>493071725.36</v>
       </c>
       <c r="E5" t="n">
-        <v>57580636.82</v>
+        <v>-30312572</v>
       </c>
       <c r="F5" t="n">
-        <v>57580636.82</v>
+        <v>-30312572</v>
       </c>
       <c r="G5" t="n">
-        <v>40136849.48</v>
+        <v>252977351.75</v>
       </c>
       <c r="H5" t="n">
-        <v>124707345.83</v>
+        <v>175732750.42</v>
       </c>
       <c r="I5" t="n">
-        <v>4332996852.05</v>
+        <v>6846528718.25</v>
       </c>
       <c r="J5" t="n">
-        <v>141888289.67</v>
+        <v>462759153.36</v>
       </c>
       <c r="K5" t="n">
-        <v>17180943.84</v>
+        <v>287026402.94</v>
       </c>
       <c r="L5" t="n">
-        <v>6472145.98</v>
+        <v>25158566.77</v>
       </c>
       <c r="M5" t="n">
-        <v>907210.6800000001</v>
+        <v>54552980.44</v>
       </c>
       <c r="N5" t="n">
-        <v>8331958.54</v>
+        <v>81637102.75</v>
       </c>
       <c r="O5" t="n">
-        <v>-3048628.135</v>
+        <v>275711780.75</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>4827301012.07</v>
+        <v>7740229904.03</v>
       </c>
       <c r="R5" t="n">
-        <v>14747528.24</v>
+        <v>231410568.11</v>
       </c>
       <c r="S5" t="n">
-        <v>445964994</v>
+        <v>549950765</v>
       </c>
       <c r="T5" t="n">
-        <v>445964994</v>
+        <v>549950765</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.46</v>
       </c>
       <c r="W5" t="n">
-        <v>40136849.48</v>
+        <v>252977351.75</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>40136849.48</v>
+        <v>252977351.75</v>
       </c>
       <c r="Z5" t="n">
-        <v>-66027.3</v>
+        <v>-720263.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>40202876.78</v>
+        <v>253697615.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>40202876.78</v>
+        <v>253697615.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>-23929143.62</v>
+        <v>-21224192.86</v>
       </c>
       <c r="AD5" t="n">
-        <v>16273733.16</v>
+        <v>232473422.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>-29554535.1</v>
+        <v>1062854.39</v>
       </c>
       <c r="AF5" t="n">
-        <v>-9535627</v>
+        <v>-31458607.95</v>
       </c>
       <c r="AG5" t="n">
-        <v>-7980451.26</v>
+        <v>836966.84</v>
       </c>
       <c r="AH5" t="n">
-        <v>1722126.24</v>
+        <v>17017784.97</v>
       </c>
       <c r="AI5" t="n">
-        <v>15793952.02</v>
+        <v>13603856.14</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6472145.98</v>
+        <v>25158566.77</v>
       </c>
       <c r="AK5" t="n">
-        <v>952601.88</v>
+        <v>1925555.54</v>
       </c>
       <c r="AL5" t="n">
-        <v>907210.6800000001</v>
+        <v>54552980.44</v>
       </c>
       <c r="AM5" t="n">
-        <v>8331958.54</v>
+        <v>81637102.75</v>
       </c>
       <c r="AN5" t="n">
-        <v>-11915102.26</v>
+        <v>161112979.1</v>
       </c>
       <c r="AO5" t="n">
-        <v>494304160.02</v>
+        <v>893701185.78</v>
       </c>
       <c r="AP5" t="n">
-        <v>28073861.71</v>
+        <v>35759423.21</v>
       </c>
       <c r="AQ5" t="n">
-        <v>28357337.87</v>
+        <v>40311911.35</v>
       </c>
       <c r="AR5" t="n">
-        <v>28357337.87</v>
+        <v>40311911.35</v>
       </c>
       <c r="AS5" t="n">
-        <v>252387263.32</v>
+        <v>455089715.18</v>
       </c>
       <c r="AT5" t="n">
-        <v>51984818.54</v>
+        <v>104798550.33</v>
       </c>
       <c r="AU5" t="n">
-        <v>13199903.16</v>
+        <v>49142916.21</v>
       </c>
       <c r="AV5" t="n">
-        <v>38784915.38</v>
+        <v>55655634.12</v>
       </c>
       <c r="AW5" t="n">
-        <v>482389057.76</v>
+        <v>1054814164.88</v>
       </c>
       <c r="AX5" t="n">
-        <v>4332996852.05</v>
+        <v>6846528718.25</v>
       </c>
       <c r="AY5" t="n">
-        <v>4815385909.81</v>
+        <v>7901342883.13</v>
       </c>
     </row>
   </sheetData>
@@ -1672,886 +1672,886 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>562483132</v>
+        <v>468383913</v>
       </c>
       <c r="C2" t="n">
-        <v>562483132</v>
+        <v>468383913</v>
       </c>
       <c r="D2" t="n">
-        <v>671253187.05</v>
+        <v>439012590.19</v>
       </c>
       <c r="E2" t="n">
-        <v>2758165204.15</v>
+        <v>1308243438.14</v>
       </c>
       <c r="F2" t="n">
-        <v>4003710240.35</v>
+        <v>1842000494.84</v>
       </c>
       <c r="G2" t="n">
-        <v>6777962746.17</v>
+        <v>3124175010</v>
       </c>
       <c r="H2" t="n">
-        <v>1132980396.78</v>
+        <v>731726257.8099999</v>
       </c>
       <c r="I2" t="n">
-        <v>4003710240.35</v>
+        <v>1842000494.84</v>
       </c>
       <c r="J2" t="n">
-        <v>46397199.15</v>
+        <v>10446759.02</v>
       </c>
       <c r="K2" t="n">
-        <v>4276581854.34</v>
+        <v>1988566033.64</v>
       </c>
       <c r="L2" t="n">
-        <v>4276581854.34</v>
+        <v>2272727831.19</v>
       </c>
       <c r="M2" t="n">
-        <v>4280099026.63</v>
+        <v>1990897567.33</v>
       </c>
       <c r="N2" t="n">
-        <v>3517172.29</v>
+        <v>2331533.69</v>
       </c>
       <c r="O2" t="n">
-        <v>4276581854.34</v>
+        <v>1988566033.64</v>
       </c>
       <c r="P2" t="n">
-        <v>163998385.13</v>
+        <v>170008052.37</v>
       </c>
       <c r="Q2" t="n">
-        <v>1488744756.65</v>
+        <v>713582106.73</v>
       </c>
       <c r="R2" t="n">
-        <v>2037503994.4</v>
+        <v>821690241.2</v>
       </c>
       <c r="S2" t="n">
-        <v>562483132</v>
+        <v>468383913</v>
       </c>
       <c r="T2" t="n">
-        <v>562483132</v>
+        <v>468383913</v>
       </c>
       <c r="U2" t="n">
-        <v>5203684245.74</v>
+        <v>2856932042.83</v>
       </c>
       <c r="V2" t="n">
-        <v>106172134.52</v>
+        <v>353987302.26</v>
       </c>
       <c r="W2" t="n">
-        <v>12987172.11</v>
+        <v>27620067.07</v>
       </c>
       <c r="X2" t="n">
-        <v>45253603.16</v>
+        <v>30023672.08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1534160.1</v>
+        <v>1735006.54</v>
       </c>
       <c r="Z2" t="n">
-        <v>46397199.15</v>
+        <v>294608556.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>46397199.15</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
+        <v>10446759.02</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>284161797.55</v>
+      </c>
       <c r="AC2" t="n">
-        <v>5097512111.22</v>
+        <v>2502944740.57</v>
       </c>
       <c r="AD2" t="n">
-        <v>3164839.05</v>
+        <v>713226.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>2711768005</v>
+        <v>1013634881.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>2501380891.83</v>
+        <v>851447178.8099999</v>
       </c>
       <c r="AG2" t="n">
-        <v>2194633666.19</v>
+        <v>1440750037</v>
       </c>
       <c r="AH2" t="n">
-        <v>331428116.14</v>
-      </c>
-      <c r="AI2" t="inlineStr"/>
+        <v>179638907.41</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ2" t="n">
-        <v>24912798.94</v>
+        <v>29072893.44</v>
       </c>
       <c r="AK2" t="n">
-        <v>1838292751.11</v>
+        <v>1232038236.15</v>
       </c>
       <c r="AL2" t="n">
-        <v>9483783272.370001</v>
+        <v>4847829610.16</v>
       </c>
       <c r="AM2" t="n">
-        <v>3253290764.37</v>
+        <v>1613158611.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>32523647.69</v>
+        <v>31841320.29</v>
       </c>
       <c r="AO2" t="n">
-        <v>40728300.77</v>
+        <v>8539731.300000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>153340078.37</v>
+        <v>83476497.56999999</v>
       </c>
       <c r="AQ2" t="n">
-        <v>990812071.03</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>940898722.1799999</v>
-      </c>
+        <v>89704249.13</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>49913348.85</v>
+        <v>89704249.13</v>
       </c>
       <c r="AT2" t="n">
-        <v>618759780.51</v>
+        <v>374366440.46</v>
       </c>
       <c r="AU2" t="n">
-        <v>69069457.27</v>
+        <v>96997604.29000001</v>
       </c>
       <c r="AV2" t="n">
-        <v>272871613.99</v>
+        <v>146565538.8</v>
       </c>
       <c r="AW2" t="n">
-        <v>272871613.99</v>
+        <v>146565538.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>1075137366.68</v>
+        <v>780151718.95</v>
       </c>
       <c r="AY2" t="n">
-        <v>-1033381446.44</v>
+        <v>-732006047.16</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2108518813.12</v>
+        <v>1512157766.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>156840079.77</v>
+        <v>18994550.66</v>
       </c>
       <c r="BB2" t="n">
-        <v>319776241.41</v>
+        <v>185664676.67</v>
       </c>
       <c r="BC2" t="n">
-        <v>819386832.1</v>
+        <v>576076863.64</v>
       </c>
       <c r="BD2" t="n">
-        <v>812515659.84</v>
+        <v>731421675.14</v>
       </c>
       <c r="BE2" t="n">
-        <v>6230492508</v>
+        <v>3234670998.38</v>
       </c>
       <c r="BF2" t="n">
-        <v>690147802.97</v>
+        <v>27033476.66</v>
       </c>
       <c r="BG2" t="n">
-        <v>11902525.97</v>
+        <v>40207.83</v>
       </c>
       <c r="BH2" t="n">
-        <v>51953055.32</v>
+        <v>51475120.41</v>
       </c>
       <c r="BI2" t="n">
-        <v>1155384391.46</v>
+        <v>863448593.4299999</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>637727253.61</v>
+        <v>350379597.72</v>
       </c>
       <c r="BL2" t="n">
-        <v>151945196.53</v>
+        <v>91734266.72</v>
       </c>
       <c r="BM2" t="n">
-        <v>365711941.32</v>
+        <v>421334728.99</v>
       </c>
       <c r="BN2" t="n">
-        <v>287443174.3</v>
+        <v>116956286.85</v>
       </c>
       <c r="BO2" t="n">
-        <v>1960347403.21</v>
+        <v>1352828714.33</v>
       </c>
       <c r="BP2" t="n">
-        <v>-25278298.78</v>
+        <v>-19321883.28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1985625701.99</v>
+        <v>1372150597.61</v>
       </c>
       <c r="BR2" t="n">
-        <v>2073314154.77</v>
+        <v>822888598.87</v>
       </c>
       <c r="BS2" t="n">
-        <v>243186449.99</v>
+        <v>126292212.7</v>
       </c>
       <c r="BT2" t="n">
-        <v>1830127704.78</v>
+        <v>696596386.17</v>
       </c>
       <c r="BU2" t="n">
-        <v>82025035.16</v>
+        <v>36990347.66</v>
       </c>
       <c r="BV2" t="n">
-        <v>1748102669.62</v>
+        <v>659606038.51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>568102832</v>
+        <v>468383913</v>
       </c>
       <c r="C3" t="n">
-        <v>568102832</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>468383913</v>
+      </c>
+      <c r="D3" t="n">
+        <v>377556929.22</v>
+      </c>
       <c r="E3" t="n">
-        <v>1593955777.76</v>
+        <v>1465028149.15</v>
       </c>
       <c r="F3" t="n">
-        <v>3817598849.89</v>
+        <v>2020794196.5</v>
       </c>
       <c r="G3" t="n">
-        <v>5230610208.43</v>
+        <v>3384801923.73</v>
       </c>
       <c r="H3" t="n">
-        <v>2011035358.54</v>
+        <v>1035530212.32</v>
       </c>
       <c r="I3" t="n">
-        <v>3817598849.89</v>
+        <v>2020794196.5</v>
       </c>
       <c r="J3" t="n">
-        <v>27437416.19</v>
+        <v>11663128.14</v>
       </c>
       <c r="K3" t="n">
-        <v>3946055610.44</v>
+        <v>2157303977.15</v>
       </c>
       <c r="L3" t="n">
-        <v>4151055610.44</v>
+        <v>2621645880.76</v>
       </c>
       <c r="M3" t="n">
-        <v>3948852519.12</v>
+        <v>2160296944.2</v>
       </c>
       <c r="N3" t="n">
-        <v>2796908.68</v>
+        <v>2992967.05</v>
       </c>
       <c r="O3" t="n">
-        <v>3946055610.44</v>
+        <v>2157303977.15</v>
       </c>
       <c r="P3" t="n">
-        <v>247900506.13</v>
+        <v>170008052.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>1210027980.07</v>
+        <v>876622142.63</v>
       </c>
       <c r="R3" t="n">
-        <v>2097346359.72</v>
+        <v>821690241.2</v>
       </c>
       <c r="S3" t="n">
-        <v>568102832</v>
+        <v>468383913</v>
       </c>
       <c r="T3" t="n">
-        <v>568102832</v>
+        <v>468383913</v>
       </c>
       <c r="U3" t="n">
-        <v>3044561661.47</v>
+        <v>3045313581.85</v>
       </c>
       <c r="V3" t="n">
-        <v>260419199.1</v>
+        <v>508053883.98</v>
       </c>
       <c r="W3" t="n">
-        <v>6682097.24</v>
+        <v>8243117.29</v>
       </c>
       <c r="X3" t="n">
-        <v>21295564.01</v>
+        <v>23805643.38</v>
       </c>
       <c r="Y3" t="n">
-        <v>4121.66</v>
+        <v>91.56</v>
       </c>
       <c r="Z3" t="n">
-        <v>232437416.19</v>
+        <v>476005031.75</v>
       </c>
       <c r="AA3" t="n">
-        <v>27437416.19</v>
+        <v>11663128.14</v>
       </c>
       <c r="AB3" t="n">
-        <v>205000000</v>
+        <v>464341903.61</v>
       </c>
       <c r="AC3" t="n">
-        <v>2784142462.37</v>
+        <v>2537259697.87</v>
       </c>
       <c r="AD3" t="n">
-        <v>5424905.88</v>
+        <v>22825980.02</v>
       </c>
       <c r="AE3" t="n">
-        <v>1361518361.57</v>
+        <v>989023117.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>1079554597.99</v>
+        <v>763156042.97</v>
       </c>
       <c r="AG3" t="n">
-        <v>1277723296.92</v>
+        <v>1425243930.26</v>
       </c>
       <c r="AH3" t="n">
-        <v>182597495.7</v>
-      </c>
-      <c r="AI3" t="inlineStr"/>
+        <v>211961217.73</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
       <c r="AJ3" t="n">
-        <v>13592984.87</v>
+        <v>25705353.07</v>
       </c>
       <c r="AK3" t="n">
-        <v>1081532816.35</v>
+        <v>1187577359.46</v>
       </c>
       <c r="AL3" t="n">
-        <v>6993414180.59</v>
+        <v>5205610526.05</v>
       </c>
       <c r="AM3" t="n">
-        <v>2198236359.68</v>
+        <v>1632820615.86</v>
       </c>
       <c r="AN3" t="n">
-        <v>28912010.32</v>
+        <v>29662351.79</v>
       </c>
       <c r="AO3" t="n">
-        <v>7900960.72</v>
+        <v>11745853.98</v>
       </c>
       <c r="AP3" t="n">
-        <v>119163672.57</v>
+        <v>106465448.52</v>
       </c>
       <c r="AQ3" t="n">
-        <v>342927437.89</v>
+        <v>88950437.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>293784447.86</v>
+        <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>49142990.03</v>
+        <v>88950437.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>629714564.0700001</v>
+        <v>386178248.99</v>
       </c>
       <c r="AU3" t="n">
-        <v>79418109.26000001</v>
+        <v>87302046.47</v>
       </c>
       <c r="AV3" t="n">
-        <v>128456760.55</v>
+        <v>136509780.65</v>
       </c>
       <c r="AW3" t="n">
-        <v>128456760.55</v>
+        <v>136509780.65</v>
       </c>
       <c r="AX3" t="n">
-        <v>861561937.39</v>
+        <v>785676646.66</v>
       </c>
       <c r="AY3" t="n">
-        <v>-927682510.41</v>
+        <v>-835175129.88</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1789244447.8</v>
+        <v>1620851776.54</v>
       </c>
       <c r="BA3" t="n">
-        <v>78179997.02</v>
+        <v>34905056.33</v>
       </c>
       <c r="BB3" t="n">
-        <v>254246988.22</v>
+        <v>200516460.22</v>
       </c>
       <c r="BC3" t="n">
-        <v>696464659.1</v>
+        <v>634599420.4299999</v>
       </c>
       <c r="BD3" t="n">
-        <v>760352803.46</v>
+        <v>750830839.5599999</v>
       </c>
       <c r="BE3" t="n">
-        <v>4795177820.91</v>
+        <v>3572789910.19</v>
       </c>
       <c r="BF3" t="n">
-        <v>87118390.38</v>
-      </c>
-      <c r="BG3" t="inlineStr"/>
+        <v>58701629.58</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>0</v>
+      </c>
       <c r="BH3" t="n">
-        <v>62403996.47</v>
+        <v>69579514.44</v>
       </c>
       <c r="BI3" t="n">
-        <v>589216952.02</v>
+        <v>761168073.55</v>
       </c>
       <c r="BJ3" t="n">
         <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>292682503.5</v>
+        <v>364172848.69</v>
       </c>
       <c r="BL3" t="n">
-        <v>78907374.86</v>
+        <v>98832276.98</v>
       </c>
       <c r="BM3" t="n">
-        <v>217627073.66</v>
+        <v>298162947.88</v>
       </c>
       <c r="BN3" t="n">
-        <v>109287247.02</v>
+        <v>149828417.86</v>
       </c>
       <c r="BO3" t="n">
-        <v>1384509617.36</v>
+        <v>1667054898.65</v>
       </c>
       <c r="BP3" t="n">
-        <v>-22803601.66</v>
+        <v>-32299434.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1407313219.02</v>
+        <v>1699354333.47</v>
       </c>
       <c r="BR3" t="n">
-        <v>2562641617.66</v>
+        <v>866457376.11</v>
       </c>
       <c r="BS3" t="n">
-        <v>401827.86</v>
+        <v>16516358.75</v>
       </c>
       <c r="BT3" t="n">
-        <v>2562239789.8</v>
+        <v>849941017.36</v>
       </c>
       <c r="BU3" t="n">
-        <v>48591240.76</v>
+        <v>36401546.4</v>
       </c>
       <c r="BV3" t="n">
-        <v>2513648549.04</v>
+        <v>813539470.96</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>468383913</v>
+        <v>568102832</v>
       </c>
       <c r="C4" t="n">
-        <v>468383913</v>
-      </c>
-      <c r="D4" t="n">
-        <v>377556929.22</v>
-      </c>
+        <v>568102832</v>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>1465028149.15</v>
+        <v>1593955777.76</v>
       </c>
       <c r="F4" t="n">
-        <v>2020794196.5</v>
+        <v>3817598849.89</v>
       </c>
       <c r="G4" t="n">
-        <v>3384801923.73</v>
+        <v>5230610208.43</v>
       </c>
       <c r="H4" t="n">
-        <v>1035530212.32</v>
+        <v>2011035358.54</v>
       </c>
       <c r="I4" t="n">
-        <v>2020794196.5</v>
+        <v>3817598849.89</v>
       </c>
       <c r="J4" t="n">
-        <v>11663128.14</v>
+        <v>27437416.19</v>
       </c>
       <c r="K4" t="n">
-        <v>2157303977.15</v>
+        <v>3946055610.44</v>
       </c>
       <c r="L4" t="n">
-        <v>2621645880.76</v>
+        <v>4151055610.44</v>
       </c>
       <c r="M4" t="n">
-        <v>2160296944.2</v>
+        <v>3948852519.12</v>
       </c>
       <c r="N4" t="n">
-        <v>2992967.05</v>
+        <v>2796908.68</v>
       </c>
       <c r="O4" t="n">
-        <v>2157303977.15</v>
+        <v>3946055610.44</v>
       </c>
       <c r="P4" t="n">
-        <v>170008052.37</v>
+        <v>247900506.13</v>
       </c>
       <c r="Q4" t="n">
-        <v>876622142.63</v>
+        <v>1210027980.07</v>
       </c>
       <c r="R4" t="n">
-        <v>821690241.2</v>
+        <v>2097346359.72</v>
       </c>
       <c r="S4" t="n">
-        <v>468383913</v>
+        <v>568102832</v>
       </c>
       <c r="T4" t="n">
-        <v>468383913</v>
+        <v>568102832</v>
       </c>
       <c r="U4" t="n">
-        <v>3045313581.85</v>
+        <v>3044561661.47</v>
       </c>
       <c r="V4" t="n">
-        <v>508053883.98</v>
+        <v>260419199.1</v>
       </c>
       <c r="W4" t="n">
-        <v>8243117.29</v>
+        <v>6682097.24</v>
       </c>
       <c r="X4" t="n">
-        <v>23805643.38</v>
+        <v>21295564.01</v>
       </c>
       <c r="Y4" t="n">
-        <v>91.56</v>
+        <v>4121.66</v>
       </c>
       <c r="Z4" t="n">
-        <v>476005031.75</v>
+        <v>232437416.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>11663128.14</v>
+        <v>27437416.19</v>
       </c>
       <c r="AB4" t="n">
-        <v>464341903.61</v>
+        <v>205000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>2537259697.87</v>
+        <v>2784142462.37</v>
       </c>
       <c r="AD4" t="n">
-        <v>22825980.02</v>
+        <v>5424905.88</v>
       </c>
       <c r="AE4" t="n">
-        <v>989023117.4</v>
+        <v>1361518361.57</v>
       </c>
       <c r="AF4" t="n">
-        <v>763156042.97</v>
+        <v>1079554597.99</v>
       </c>
       <c r="AG4" t="n">
-        <v>1425243930.26</v>
+        <v>1277723296.92</v>
       </c>
       <c r="AH4" t="n">
-        <v>211961217.73</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
-      </c>
+        <v>182597495.7</v>
+      </c>
+      <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="n">
-        <v>25705353.07</v>
+        <v>13592984.87</v>
       </c>
       <c r="AK4" t="n">
-        <v>1187577359.46</v>
+        <v>1081532816.35</v>
       </c>
       <c r="AL4" t="n">
-        <v>5205610526.05</v>
+        <v>6993414180.59</v>
       </c>
       <c r="AM4" t="n">
-        <v>1632820615.86</v>
+        <v>2198236359.68</v>
       </c>
       <c r="AN4" t="n">
-        <v>29662351.79</v>
+        <v>28912010.32</v>
       </c>
       <c r="AO4" t="n">
-        <v>11745853.98</v>
+        <v>7900960.72</v>
       </c>
       <c r="AP4" t="n">
-        <v>106465448.52</v>
+        <v>119163672.57</v>
       </c>
       <c r="AQ4" t="n">
-        <v>88950437.5</v>
+        <v>342927437.89</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>293784447.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>88950437.5</v>
+        <v>49142990.03</v>
       </c>
       <c r="AT4" t="n">
-        <v>386178248.99</v>
+        <v>629714564.0700001</v>
       </c>
       <c r="AU4" t="n">
-        <v>87302046.47</v>
+        <v>79418109.26000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>136509780.65</v>
+        <v>128456760.55</v>
       </c>
       <c r="AW4" t="n">
-        <v>136509780.65</v>
+        <v>128456760.55</v>
       </c>
       <c r="AX4" t="n">
-        <v>785676646.66</v>
+        <v>861561937.39</v>
       </c>
       <c r="AY4" t="n">
-        <v>-835175129.88</v>
+        <v>-927682510.41</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1620851776.54</v>
+        <v>1789244447.8</v>
       </c>
       <c r="BA4" t="n">
-        <v>34905056.33</v>
+        <v>78179997.02</v>
       </c>
       <c r="BB4" t="n">
-        <v>200516460.22</v>
+        <v>254246988.22</v>
       </c>
       <c r="BC4" t="n">
-        <v>634599420.4299999</v>
+        <v>696464659.1</v>
       </c>
       <c r="BD4" t="n">
-        <v>750830839.5599999</v>
+        <v>760352803.46</v>
       </c>
       <c r="BE4" t="n">
-        <v>3572789910.19</v>
+        <v>4795177820.91</v>
       </c>
       <c r="BF4" t="n">
-        <v>58701629.58</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
+        <v>87118390.38</v>
+      </c>
+      <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="n">
-        <v>69579514.44</v>
+        <v>62403996.47</v>
       </c>
       <c r="BI4" t="n">
-        <v>761168073.55</v>
+        <v>589216952.02</v>
       </c>
       <c r="BJ4" t="n">
         <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>364172848.69</v>
+        <v>292682503.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>98832276.98</v>
+        <v>78907374.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>298162947.88</v>
+        <v>217627073.66</v>
       </c>
       <c r="BN4" t="n">
-        <v>149828417.86</v>
+        <v>109287247.02</v>
       </c>
       <c r="BO4" t="n">
-        <v>1667054898.65</v>
+        <v>1384509617.36</v>
       </c>
       <c r="BP4" t="n">
-        <v>-32299434.82</v>
+        <v>-22803601.66</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1699354333.47</v>
+        <v>1407313219.02</v>
       </c>
       <c r="BR4" t="n">
-        <v>866457376.11</v>
+        <v>2562641617.66</v>
       </c>
       <c r="BS4" t="n">
-        <v>16516358.75</v>
+        <v>401827.86</v>
       </c>
       <c r="BT4" t="n">
-        <v>849941017.36</v>
+        <v>2562239789.8</v>
       </c>
       <c r="BU4" t="n">
-        <v>36401546.4</v>
+        <v>48591240.76</v>
       </c>
       <c r="BV4" t="n">
-        <v>813539470.96</v>
+        <v>2513648549.04</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>468383913</v>
+        <v>562483132</v>
       </c>
       <c r="C5" t="n">
-        <v>468383913</v>
+        <v>562483132</v>
       </c>
       <c r="D5" t="n">
-        <v>439012590.19</v>
+        <v>671253187.05</v>
       </c>
       <c r="E5" t="n">
-        <v>1308243438.14</v>
+        <v>2758165204.15</v>
       </c>
       <c r="F5" t="n">
-        <v>1842000494.84</v>
+        <v>4003710240.35</v>
       </c>
       <c r="G5" t="n">
-        <v>3124175010</v>
+        <v>6777962746.17</v>
       </c>
       <c r="H5" t="n">
-        <v>731726257.8099999</v>
+        <v>1132980396.78</v>
       </c>
       <c r="I5" t="n">
-        <v>1842000494.84</v>
+        <v>4003710240.35</v>
       </c>
       <c r="J5" t="n">
-        <v>10446759.02</v>
+        <v>46397199.15</v>
       </c>
       <c r="K5" t="n">
-        <v>1988566033.64</v>
+        <v>4276581854.34</v>
       </c>
       <c r="L5" t="n">
-        <v>2272727831.19</v>
+        <v>4276581854.34</v>
       </c>
       <c r="M5" t="n">
-        <v>1990897567.33</v>
+        <v>4280099026.63</v>
       </c>
       <c r="N5" t="n">
-        <v>2331533.69</v>
+        <v>3517172.29</v>
       </c>
       <c r="O5" t="n">
-        <v>1988566033.64</v>
+        <v>4276581854.34</v>
       </c>
       <c r="P5" t="n">
-        <v>170008052.37</v>
+        <v>163998385.13</v>
       </c>
       <c r="Q5" t="n">
-        <v>713582106.73</v>
+        <v>1488744756.65</v>
       </c>
       <c r="R5" t="n">
-        <v>821690241.2</v>
+        <v>2037503994.4</v>
       </c>
       <c r="S5" t="n">
-        <v>468383913</v>
+        <v>562483132</v>
       </c>
       <c r="T5" t="n">
-        <v>468383913</v>
+        <v>562483132</v>
       </c>
       <c r="U5" t="n">
-        <v>2856932042.83</v>
+        <v>5203684245.74</v>
       </c>
       <c r="V5" t="n">
-        <v>353987302.26</v>
+        <v>106172134.52</v>
       </c>
       <c r="W5" t="n">
-        <v>27620067.07</v>
+        <v>12987172.11</v>
       </c>
       <c r="X5" t="n">
-        <v>30023672.08</v>
+        <v>45253603.16</v>
       </c>
       <c r="Y5" t="n">
-        <v>1735006.54</v>
+        <v>1534160.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>294608556.57</v>
+        <v>46397199.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>10446759.02</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>284161797.55</v>
-      </c>
+        <v>46397199.15</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>2502944740.57</v>
+        <v>5097512111.22</v>
       </c>
       <c r="AD5" t="n">
-        <v>713226.7</v>
+        <v>3164839.05</v>
       </c>
       <c r="AE5" t="n">
-        <v>1013634881.57</v>
+        <v>2711768005</v>
       </c>
       <c r="AF5" t="n">
-        <v>851447178.8099999</v>
+        <v>2501380891.83</v>
       </c>
       <c r="AG5" t="n">
-        <v>1440750037</v>
+        <v>2194633666.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>179638907.41</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
-      </c>
+        <v>331428116.14</v>
+      </c>
+      <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>29072893.44</v>
+        <v>24912798.94</v>
       </c>
       <c r="AK5" t="n">
-        <v>1232038236.15</v>
+        <v>1838292751.11</v>
       </c>
       <c r="AL5" t="n">
-        <v>4847829610.16</v>
+        <v>9483783272.370001</v>
       </c>
       <c r="AM5" t="n">
-        <v>1613158611.78</v>
+        <v>3253290764.37</v>
       </c>
       <c r="AN5" t="n">
-        <v>31841320.29</v>
+        <v>32523647.69</v>
       </c>
       <c r="AO5" t="n">
-        <v>8539731.300000001</v>
+        <v>40728300.77</v>
       </c>
       <c r="AP5" t="n">
-        <v>83476497.56999999</v>
+        <v>153340078.37</v>
       </c>
       <c r="AQ5" t="n">
-        <v>89704249.13</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>990812071.03</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>940898722.1799999</v>
+      </c>
       <c r="AS5" t="n">
-        <v>89704249.13</v>
+        <v>49913348.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>374366440.46</v>
+        <v>618759780.51</v>
       </c>
       <c r="AU5" t="n">
-        <v>96997604.29000001</v>
+        <v>69069457.27</v>
       </c>
       <c r="AV5" t="n">
-        <v>146565538.8</v>
+        <v>272871613.99</v>
       </c>
       <c r="AW5" t="n">
-        <v>146565538.8</v>
+        <v>272871613.99</v>
       </c>
       <c r="AX5" t="n">
-        <v>780151718.95</v>
+        <v>1075137366.68</v>
       </c>
       <c r="AY5" t="n">
-        <v>-732006047.16</v>
+        <v>-1033381446.44</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1512157766.11</v>
+        <v>2108518813.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>18994550.66</v>
+        <v>156840079.77</v>
       </c>
       <c r="BB5" t="n">
-        <v>185664676.67</v>
+        <v>319776241.41</v>
       </c>
       <c r="BC5" t="n">
-        <v>576076863.64</v>
+        <v>819386832.1</v>
       </c>
       <c r="BD5" t="n">
-        <v>731421675.14</v>
+        <v>812515659.84</v>
       </c>
       <c r="BE5" t="n">
-        <v>3234670998.38</v>
+        <v>6230492508</v>
       </c>
       <c r="BF5" t="n">
-        <v>27033476.66</v>
+        <v>690147802.97</v>
       </c>
       <c r="BG5" t="n">
-        <v>40207.83</v>
+        <v>11902525.97</v>
       </c>
       <c r="BH5" t="n">
-        <v>51475120.41</v>
+        <v>51953055.32</v>
       </c>
       <c r="BI5" t="n">
-        <v>863448593.4299999</v>
+        <v>1155384391.46</v>
       </c>
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>350379597.72</v>
+        <v>637727253.61</v>
       </c>
       <c r="BL5" t="n">
-        <v>91734266.72</v>
+        <v>151945196.53</v>
       </c>
       <c r="BM5" t="n">
-        <v>421334728.99</v>
+        <v>365711941.32</v>
       </c>
       <c r="BN5" t="n">
-        <v>116956286.85</v>
+        <v>287443174.3</v>
       </c>
       <c r="BO5" t="n">
-        <v>1352828714.33</v>
+        <v>1960347403.21</v>
       </c>
       <c r="BP5" t="n">
-        <v>-19321883.28</v>
+        <v>-25278298.78</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1372150597.61</v>
+        <v>1985625701.99</v>
       </c>
       <c r="BR5" t="n">
-        <v>822888598.87</v>
+        <v>2073314154.77</v>
       </c>
       <c r="BS5" t="n">
-        <v>126292212.7</v>
+        <v>243186449.99</v>
       </c>
       <c r="BT5" t="n">
-        <v>696596386.17</v>
+        <v>1830127704.78</v>
       </c>
       <c r="BU5" t="n">
-        <v>36990347.66</v>
+        <v>82025035.16</v>
       </c>
       <c r="BV5" t="n">
-        <v>659606038.51</v>
+        <v>1748102669.62</v>
       </c>
     </row>
   </sheetData>
@@ -2807,578 +2807,578 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-431943078.83</v>
+        <v>-333702589.32</v>
       </c>
       <c r="C2" t="n">
-        <v>-2357281342.51</v>
+        <v>-1040653781.77</v>
       </c>
       <c r="D2" t="n">
-        <v>3498275975.35</v>
+        <v>1436501419.57</v>
       </c>
       <c r="E2" t="n">
-        <v>-583643629.1900001</v>
+        <v>-205517179.44</v>
       </c>
       <c r="F2" t="n">
-        <v>1748105621.03</v>
+        <v>659610410.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2513651495.3</v>
+        <v>562275619.37</v>
       </c>
       <c r="H2" t="n">
-        <v>2903306.16</v>
+        <v>-2480687.36</v>
       </c>
       <c r="I2" t="n">
-        <v>-768449180.4299999</v>
+        <v>99815478.90000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1097361033.28</v>
+        <v>282905665.06</v>
       </c>
       <c r="K2" t="n">
-        <v>13798041.75</v>
+        <v>-82148665.26000001</v>
       </c>
       <c r="L2" t="n">
-        <v>-57431641.31</v>
+        <v>-30793307.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1140994632.84</v>
+        <v>395847637.8</v>
       </c>
       <c r="N2" t="n">
-        <v>1140994632.84</v>
+        <v>395847637.8</v>
       </c>
       <c r="O2" t="n">
-        <v>-2357281342.51</v>
+        <v>-1040653781.77</v>
       </c>
       <c r="P2" t="n">
-        <v>3498275975.35</v>
+        <v>1436501419.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2017510764.07</v>
+        <v>-54904776.28</v>
       </c>
       <c r="R2" t="n">
-        <v>-50000000</v>
+        <v>-62126125</v>
       </c>
       <c r="S2" t="n">
-        <v>-1425167185.66</v>
+        <v>141447043.96</v>
       </c>
       <c r="T2" t="n">
-        <v>376520118.77</v>
+        <v>1099259044.81</v>
       </c>
       <c r="U2" t="n">
-        <v>-1801687304.43</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
+        <v>-957812000.85</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8418695.470000001</v>
+      </c>
+      <c r="W2" t="n">
+        <v>8418695.470000001</v>
+      </c>
       <c r="X2" t="n">
-        <v>-542343578.41</v>
+        <v>-142644390.71</v>
       </c>
       <c r="Y2" t="n">
-        <v>41300050.78</v>
+        <v>62872788.73</v>
       </c>
       <c r="Z2" t="n">
-        <v>-583643629.1900001</v>
+        <v>-205517179.44</v>
       </c>
       <c r="AA2" t="n">
-        <v>151700550.36</v>
+        <v>-128185409.88</v>
       </c>
       <c r="AB2" t="n">
-        <v>-294783925.83</v>
+        <v>-341889085.93</v>
       </c>
       <c r="AC2" t="n">
-        <v>-32646367.36</v>
+        <v>-31227605.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>998482329.5599999</v>
+        <v>135183786.7</v>
       </c>
       <c r="AE2" t="n">
-        <v>-576212805.25</v>
+        <v>-199320877.31</v>
       </c>
       <c r="AF2" t="n">
-        <v>-684407082.78</v>
+        <v>-246524389.93</v>
       </c>
       <c r="AG2" t="n">
-        <v>-13884638.53</v>
+        <v>36396856.84</v>
       </c>
       <c r="AH2" t="n">
-        <v>175732750.42</v>
+        <v>124707345.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>11592807.48</v>
+        <v>18345865.93</v>
       </c>
       <c r="AJ2" t="n">
-        <v>164139942.94</v>
+        <v>106361479.9</v>
       </c>
       <c r="AK2" t="n">
-        <v>-3294411.8</v>
+        <v>-6101541.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>2692607.62</v>
+        <v>-6978729.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>253697615.36</v>
+        <v>40202876.78</v>
       </c>
       <c r="AN2" t="n">
-        <v>151700550.36</v>
+        <v>-128185409.88</v>
       </c>
       <c r="AO2" t="n">
-        <v>343722684.34</v>
+        <v>225417311.79</v>
       </c>
       <c r="AP2" t="n">
-        <v>-8169399165.41</v>
+        <v>-5640143960.94</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-495642736.95</v>
+        <v>-410767131.93</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1155234293.89</v>
+        <v>-839874673.84</v>
       </c>
       <c r="AS2" t="n">
-        <v>-6518522134.57</v>
+        <v>-4389502155.17</v>
       </c>
       <c r="AT2" t="n">
-        <v>7977377031.43</v>
+        <v>5286541239.27</v>
       </c>
       <c r="AU2" t="n">
-        <v>417207689.82</v>
+        <v>450635989.98</v>
       </c>
       <c r="AV2" t="n">
-        <v>7560169341.61</v>
+        <v>4835905249.29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>590611080.75</v>
+        <v>-97664290.09999999</v>
       </c>
       <c r="C3" t="n">
-        <v>-1388307374.83</v>
+        <v>-1121056001</v>
       </c>
       <c r="D3" t="n">
-        <v>1500129415.26</v>
+        <v>1243091103.73</v>
       </c>
       <c r="E3" t="n">
-        <v>-230512452.64</v>
+        <v>-150271474.54</v>
       </c>
       <c r="F3" t="n">
-        <v>2513651495.3</v>
+        <v>813543851.1</v>
       </c>
       <c r="G3" t="n">
-        <v>813543851.1</v>
+        <v>659610410.91</v>
       </c>
       <c r="H3" t="n">
-        <v>1028978.26</v>
+        <v>15860492.42</v>
       </c>
       <c r="I3" t="n">
-        <v>1699078665.94</v>
+        <v>138072947.77</v>
       </c>
       <c r="J3" t="n">
-        <v>1340739810.54</v>
+        <v>118077432.9</v>
       </c>
       <c r="K3" t="n">
-        <v>1269150023.34</v>
+        <v>36519384.49</v>
       </c>
       <c r="L3" t="n">
-        <v>-40232253.23</v>
+        <v>-40477054.32</v>
       </c>
       <c r="M3" t="n">
-        <v>111822040.43</v>
+        <v>122035102.73</v>
       </c>
       <c r="N3" t="n">
-        <v>111822040.43</v>
+        <v>122035102.73</v>
       </c>
       <c r="O3" t="n">
-        <v>-1388307374.83</v>
+        <v>-1121056001</v>
       </c>
       <c r="P3" t="n">
-        <v>1500129415.26</v>
+        <v>1243091103.73</v>
       </c>
       <c r="Q3" t="n">
-        <v>-462784677.99</v>
+        <v>-32611669.57</v>
       </c>
       <c r="R3" t="n">
-        <v>5017359.29</v>
+        <v>-4563498.37</v>
       </c>
       <c r="S3" t="n">
-        <v>-263906914.89</v>
+        <v>112709242.41</v>
       </c>
       <c r="T3" t="n">
-        <v>311252394.09</v>
+        <v>363809242.41</v>
       </c>
       <c r="U3" t="n">
-        <v>-575159308.98</v>
-      </c>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
+        <v>-251100000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
       <c r="X3" t="n">
-        <v>-203895122.39</v>
+        <v>-140757413.61</v>
       </c>
       <c r="Y3" t="n">
-        <v>26617330.25</v>
+        <v>9514060.93</v>
       </c>
       <c r="Z3" t="n">
-        <v>-230512452.64</v>
+        <v>-150271474.54</v>
       </c>
       <c r="AA3" t="n">
-        <v>821123533.39</v>
+        <v>52607184.44</v>
       </c>
       <c r="AB3" t="n">
-        <v>373947492.71</v>
+        <v>-296924356.84</v>
       </c>
       <c r="AC3" t="n">
-        <v>-12694193.95</v>
+        <v>-24489430.01</v>
       </c>
       <c r="AD3" t="n">
-        <v>-55744011.86</v>
+        <v>-28193039.61</v>
       </c>
       <c r="AE3" t="n">
-        <v>145003144.12</v>
+        <v>66877747.09</v>
       </c>
       <c r="AF3" t="n">
-        <v>297382554.4</v>
+        <v>-311119634.31</v>
       </c>
       <c r="AG3" t="n">
-        <v>33794346.21</v>
+        <v>-27253456.84</v>
       </c>
       <c r="AH3" t="n">
-        <v>153727732.91</v>
+        <v>149628265.88</v>
       </c>
       <c r="AI3" t="n">
-        <v>10166655.92</v>
+        <v>14292601.35</v>
       </c>
       <c r="AJ3" t="n">
-        <v>143561076.99</v>
+        <v>135335664.53</v>
       </c>
       <c r="AK3" t="n">
-        <v>-122574314.48</v>
+        <v>-5195826.69</v>
       </c>
       <c r="AL3" t="n">
-        <v>-3999692.05</v>
+        <v>-915276.91</v>
       </c>
       <c r="AM3" t="n">
-        <v>360960071.81</v>
+        <v>178985186.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>821123533.39</v>
+        <v>52607184.44</v>
       </c>
       <c r="AO3" t="n">
-        <v>333042715.26</v>
+        <v>247821501.28</v>
       </c>
       <c r="AP3" t="n">
-        <v>-6036551966.14</v>
+        <v>-6249400076.73</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-259656985.7</v>
+        <v>-232263734.77</v>
       </c>
       <c r="AR3" t="n">
-        <v>-797365853.9</v>
+        <v>-865656957.9299999</v>
       </c>
       <c r="AS3" t="n">
-        <v>-4979529126.54</v>
+        <v>-5151479384.03</v>
       </c>
       <c r="AT3" t="n">
-        <v>6524632784.27</v>
+        <v>6054185759.89</v>
       </c>
       <c r="AU3" t="n">
-        <v>122977007.74</v>
+        <v>130186429.68</v>
       </c>
       <c r="AV3" t="n">
-        <v>6401655776.53</v>
+        <v>5923999330.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-97664290.09999999</v>
+        <v>590611080.75</v>
       </c>
       <c r="C4" t="n">
-        <v>-1121056001</v>
+        <v>-1388307374.83</v>
       </c>
       <c r="D4" t="n">
-        <v>1243091103.73</v>
+        <v>1500129415.26</v>
       </c>
       <c r="E4" t="n">
-        <v>-150271474.54</v>
+        <v>-230512452.64</v>
       </c>
       <c r="F4" t="n">
+        <v>2513651495.3</v>
+      </c>
+      <c r="G4" t="n">
         <v>813543851.1</v>
       </c>
-      <c r="G4" t="n">
-        <v>659610410.91</v>
-      </c>
       <c r="H4" t="n">
-        <v>15860492.42</v>
+        <v>1028978.26</v>
       </c>
       <c r="I4" t="n">
-        <v>138072947.77</v>
+        <v>1699078665.94</v>
       </c>
       <c r="J4" t="n">
-        <v>118077432.9</v>
+        <v>1340739810.54</v>
       </c>
       <c r="K4" t="n">
-        <v>36519384.49</v>
+        <v>1269150023.34</v>
       </c>
       <c r="L4" t="n">
-        <v>-40477054.32</v>
+        <v>-40232253.23</v>
       </c>
       <c r="M4" t="n">
-        <v>122035102.73</v>
+        <v>111822040.43</v>
       </c>
       <c r="N4" t="n">
-        <v>122035102.73</v>
+        <v>111822040.43</v>
       </c>
       <c r="O4" t="n">
-        <v>-1121056001</v>
+        <v>-1388307374.83</v>
       </c>
       <c r="P4" t="n">
-        <v>1243091103.73</v>
+        <v>1500129415.26</v>
       </c>
       <c r="Q4" t="n">
-        <v>-32611669.57</v>
+        <v>-462784677.99</v>
       </c>
       <c r="R4" t="n">
-        <v>-4563498.37</v>
+        <v>5017359.29</v>
       </c>
       <c r="S4" t="n">
-        <v>112709242.41</v>
+        <v>-263906914.89</v>
       </c>
       <c r="T4" t="n">
-        <v>363809242.41</v>
+        <v>311252394.09</v>
       </c>
       <c r="U4" t="n">
-        <v>-251100000</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
+        <v>-575159308.98</v>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
       <c r="X4" t="n">
-        <v>-140757413.61</v>
+        <v>-203895122.39</v>
       </c>
       <c r="Y4" t="n">
-        <v>9514060.93</v>
+        <v>26617330.25</v>
       </c>
       <c r="Z4" t="n">
-        <v>-150271474.54</v>
+        <v>-230512452.64</v>
       </c>
       <c r="AA4" t="n">
-        <v>52607184.44</v>
+        <v>821123533.39</v>
       </c>
       <c r="AB4" t="n">
-        <v>-296924356.84</v>
+        <v>373947492.71</v>
       </c>
       <c r="AC4" t="n">
-        <v>-24489430.01</v>
+        <v>-12694193.95</v>
       </c>
       <c r="AD4" t="n">
-        <v>-28193039.61</v>
+        <v>-55744011.86</v>
       </c>
       <c r="AE4" t="n">
-        <v>66877747.09</v>
+        <v>145003144.12</v>
       </c>
       <c r="AF4" t="n">
-        <v>-311119634.31</v>
+        <v>297382554.4</v>
       </c>
       <c r="AG4" t="n">
-        <v>-27253456.84</v>
+        <v>33794346.21</v>
       </c>
       <c r="AH4" t="n">
-        <v>149628265.88</v>
+        <v>153727732.91</v>
       </c>
       <c r="AI4" t="n">
-        <v>14292601.35</v>
+        <v>10166655.92</v>
       </c>
       <c r="AJ4" t="n">
-        <v>135335664.53</v>
+        <v>143561076.99</v>
       </c>
       <c r="AK4" t="n">
-        <v>-5195826.69</v>
+        <v>-122574314.48</v>
       </c>
       <c r="AL4" t="n">
-        <v>-915276.91</v>
+        <v>-3999692.05</v>
       </c>
       <c r="AM4" t="n">
-        <v>178985186.12</v>
+        <v>360960071.81</v>
       </c>
       <c r="AN4" t="n">
-        <v>52607184.44</v>
+        <v>821123533.39</v>
       </c>
       <c r="AO4" t="n">
-        <v>247821501.28</v>
+        <v>333042715.26</v>
       </c>
       <c r="AP4" t="n">
-        <v>-6249400076.73</v>
+        <v>-6036551966.14</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-232263734.77</v>
+        <v>-259656985.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>-865656957.9299999</v>
+        <v>-797365853.9</v>
       </c>
       <c r="AS4" t="n">
-        <v>-5151479384.03</v>
+        <v>-4979529126.54</v>
       </c>
       <c r="AT4" t="n">
-        <v>6054185759.89</v>
+        <v>6524632784.27</v>
       </c>
       <c r="AU4" t="n">
-        <v>130186429.68</v>
+        <v>122977007.74</v>
       </c>
       <c r="AV4" t="n">
-        <v>5923999330.21</v>
+        <v>6401655776.53</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-333702589.32</v>
+        <v>-431943078.83</v>
       </c>
       <c r="C5" t="n">
-        <v>-1040653781.77</v>
+        <v>-2357281342.51</v>
       </c>
       <c r="D5" t="n">
-        <v>1436501419.57</v>
+        <v>3498275975.35</v>
       </c>
       <c r="E5" t="n">
-        <v>-205517179.44</v>
+        <v>-583643629.1900001</v>
       </c>
       <c r="F5" t="n">
-        <v>659610410.91</v>
+        <v>1748105621.03</v>
       </c>
       <c r="G5" t="n">
-        <v>562275619.37</v>
+        <v>2513651495.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-2480687.36</v>
+        <v>2903306.16</v>
       </c>
       <c r="I5" t="n">
-        <v>99815478.90000001</v>
+        <v>-768449180.4299999</v>
       </c>
       <c r="J5" t="n">
-        <v>282905665.06</v>
+        <v>1097361033.28</v>
       </c>
       <c r="K5" t="n">
-        <v>-82148665.26000001</v>
+        <v>13798041.75</v>
       </c>
       <c r="L5" t="n">
-        <v>-30793307.48</v>
+        <v>-57431641.31</v>
       </c>
       <c r="M5" t="n">
-        <v>395847637.8</v>
+        <v>1140994632.84</v>
       </c>
       <c r="N5" t="n">
-        <v>395847637.8</v>
+        <v>1140994632.84</v>
       </c>
       <c r="O5" t="n">
-        <v>-1040653781.77</v>
+        <v>-2357281342.51</v>
       </c>
       <c r="P5" t="n">
-        <v>1436501419.57</v>
+        <v>3498275975.35</v>
       </c>
       <c r="Q5" t="n">
-        <v>-54904776.28</v>
+        <v>-2017510764.07</v>
       </c>
       <c r="R5" t="n">
-        <v>-62126125</v>
+        <v>-50000000</v>
       </c>
       <c r="S5" t="n">
-        <v>141447043.96</v>
+        <v>-1425167185.66</v>
       </c>
       <c r="T5" t="n">
-        <v>1099259044.81</v>
+        <v>376520118.77</v>
       </c>
       <c r="U5" t="n">
-        <v>-957812000.85</v>
-      </c>
-      <c r="V5" t="n">
-        <v>8418695.470000001</v>
-      </c>
-      <c r="W5" t="n">
-        <v>8418695.470000001</v>
-      </c>
+        <v>-1801687304.43</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
       <c r="X5" t="n">
-        <v>-142644390.71</v>
+        <v>-542343578.41</v>
       </c>
       <c r="Y5" t="n">
-        <v>62872788.73</v>
+        <v>41300050.78</v>
       </c>
       <c r="Z5" t="n">
-        <v>-205517179.44</v>
+        <v>-583643629.1900001</v>
       </c>
       <c r="AA5" t="n">
-        <v>-128185409.88</v>
+        <v>151700550.36</v>
       </c>
       <c r="AB5" t="n">
-        <v>-341889085.93</v>
+        <v>-294783925.83</v>
       </c>
       <c r="AC5" t="n">
-        <v>-31227605.39</v>
+        <v>-32646367.36</v>
       </c>
       <c r="AD5" t="n">
-        <v>135183786.7</v>
+        <v>998482329.5599999</v>
       </c>
       <c r="AE5" t="n">
-        <v>-199320877.31</v>
+        <v>-576212805.25</v>
       </c>
       <c r="AF5" t="n">
-        <v>-246524389.93</v>
+        <v>-684407082.78</v>
       </c>
       <c r="AG5" t="n">
-        <v>36396856.84</v>
+        <v>-13884638.53</v>
       </c>
       <c r="AH5" t="n">
-        <v>124707345.83</v>
+        <v>175732750.42</v>
       </c>
       <c r="AI5" t="n">
-        <v>18345865.93</v>
+        <v>11592807.48</v>
       </c>
       <c r="AJ5" t="n">
-        <v>106361479.9</v>
+        <v>164139942.94</v>
       </c>
       <c r="AK5" t="n">
-        <v>-6101541.4</v>
+        <v>-3294411.8</v>
       </c>
       <c r="AL5" t="n">
-        <v>-6978729.93</v>
+        <v>2692607.62</v>
       </c>
       <c r="AM5" t="n">
-        <v>40202876.78</v>
+        <v>253697615.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>-128185409.88</v>
+        <v>151700550.36</v>
       </c>
       <c r="AO5" t="n">
-        <v>225417311.79</v>
+        <v>343722684.34</v>
       </c>
       <c r="AP5" t="n">
-        <v>-5640143960.94</v>
+        <v>-8169399165.41</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-410767131.93</v>
+        <v>-495642736.95</v>
       </c>
       <c r="AR5" t="n">
-        <v>-839874673.84</v>
+        <v>-1155234293.89</v>
       </c>
       <c r="AS5" t="n">
-        <v>-4389502155.17</v>
+        <v>-6518522134.57</v>
       </c>
       <c r="AT5" t="n">
-        <v>5286541239.27</v>
+        <v>7977377031.43</v>
       </c>
       <c r="AU5" t="n">
-        <v>450635989.98</v>
+        <v>417207689.82</v>
       </c>
       <c r="AV5" t="n">
-        <v>4835905249.29</v>
+        <v>7560169341.61</v>
       </c>
     </row>
   </sheetData>
@@ -3943,187 +3943,187 @@
       </c>
       <c r="DF1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
         <is>
           <t>longName</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
         </is>
       </c>
       <c r="EQ1" t="inlineStr">
@@ -4228,34 +4228,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>9.52</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="V2" t="n">
-        <v>10.78</v>
+        <v>8.59</v>
       </c>
       <c r="W2" t="n">
-        <v>9.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X2" t="n">
-        <v>9.68</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.52</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="Z2" t="n">
-        <v>10.78</v>
+        <v>8.59</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.68</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AC2" t="n">
         <v>0.02</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="AE2" t="n">
         <v>1780444800</v>
@@ -4267,31 +4267,31 @@
         <v>0.9</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.446</v>
+        <v>0.308</v>
       </c>
       <c r="AI2" t="n">
-        <v>14.983606</v>
+        <v>14.114753</v>
       </c>
       <c r="AJ2" t="n">
-        <v>17916232</v>
+        <v>15728871</v>
       </c>
       <c r="AK2" t="n">
-        <v>17916232</v>
+        <v>15728871</v>
       </c>
       <c r="AL2" t="n">
-        <v>12948539</v>
+        <v>14089426</v>
       </c>
       <c r="AM2" t="n">
-        <v>18934694</v>
+        <v>14142234</v>
       </c>
       <c r="AN2" t="n">
-        <v>18934694</v>
+        <v>14142234</v>
       </c>
       <c r="AO2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="AP2" t="n">
-        <v>9.15</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -4300,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>5141095936</v>
+        <v>4842979840</v>
       </c>
       <c r="AT2" t="n">
-        <v>5141095826</v>
+        <v>4842979766</v>
       </c>
       <c r="AU2" t="n">
-        <v>9.09</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
@@ -4318,19 +4318,19 @@
         <v>2.05096</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.667202</v>
+        <v>0.62851304</v>
       </c>
       <c r="AZ2" t="n">
-        <v>11.3048</v>
+        <v>10.5224</v>
       </c>
       <c r="BA2" t="n">
-        <v>14.16775</v>
+        <v>13.59745</v>
       </c>
       <c r="BB2" t="n">
         <v>0.015</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.0015756302</v>
+        <v>0.0017421603</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -4341,13 +4341,13 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>6455664128</v>
+        <v>6157548032</v>
       </c>
       <c r="BG2" t="n">
         <v>-0.02219</v>
       </c>
       <c r="BH2" t="n">
-        <v>415371294</v>
+        <v>414505070</v>
       </c>
       <c r="BI2" t="n">
         <v>562483132</v>
@@ -4356,7 +4356,7 @@
         <v>0.27741</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.030869998</v>
+        <v>0.030840002</v>
       </c>
       <c r="BL2" t="n">
         <v>562483132</v>
@@ -4365,7 +4365,7 @@
         <v>7.53</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.2138114</v>
+        <v>1.1434262</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -4394,16 +4394,16 @@
         <v>1306454400</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.838</v>
+        <v>0.799</v>
       </c>
       <c r="BX2" t="n">
-        <v>98.04300000000001</v>
+        <v>93.51600000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.41372675</v>
+        <v>-0.4387223</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CA2" t="n">
         <v>0.015</v>
@@ -4417,7 +4417,7 @@
         </is>
       </c>
       <c r="CD2" t="n">
-        <v>9.140000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
@@ -4516,140 +4516,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>1116811800000</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="inlineStr">
+        <is>
+          <t>8.2 - 8.78</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>14089426</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.40999985</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>0.049999982</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>8.2 - 19.0</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-10.39</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.5468421</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-43.87223</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>1619693940</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.31</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>GUOGUANG ELECTRIC COMPANY LIMIT</t>
+        </is>
+      </c>
+      <c r="DW2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DX2" t="n">
+        <v>1782111888</v>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>finmb_22338267</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-1.9124002</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.18174563</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-4.9874506</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-0.36679307</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EL2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EM2" t="inlineStr">
         <is>
           <t>Guoguang Electric Company Limited</t>
         </is>
       </c>
-      <c r="DH2" t="n">
-        <v>-3.9915974</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>9.140000000000001</v>
-      </c>
-      <c r="DJ2" t="inlineStr">
-        <is>
-          <t>GUOGUANG ELECTRIC COMPANY LIMIT</t>
-        </is>
-      </c>
-      <c r="DK2" t="b">
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="EO2" t="n">
         <v>0</v>
       </c>
-      <c r="DL2" t="n">
-        <v>1116811800000</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.3800001</v>
-      </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>9.09 - 9.68</t>
-        </is>
-      </c>
-      <c r="DO2" t="inlineStr">
-        <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="DP2" t="n">
-        <v>12948539</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0.05000019</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>0.005500571</v>
-      </c>
-      <c r="DS2" t="inlineStr">
-        <is>
-          <t>9.09 - 19.0</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-9.859999999999999</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.51894736</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-41.372673</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>1619693940</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[{'header': 'Dividend', 'message': '002045.SZ announced a cash dividend of CNY 0.015 with an ex-date of Jun. 3, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1780416000000, 'amount': '0.015'}}]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1780038282</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>finmb_22338267</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="ED2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>1619693940</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-2.1647997</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.19149385</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-5.02775</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-0.35487285</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EP2" t="b">
-        <v>0</v>
+      <c r="EP2" t="n">
+        <v>8.609999999999999</v>
       </c>
       <c r="EQ2" t="inlineStr"/>
     </row>
